--- a/XlsxSharp.Tests/Resource/Examples/Styles/UsingColors.xlsx
+++ b/XlsxSharp.Tests/Resource/Examples/Styles/UsingColors.xlsx
@@ -1,57 +1,57 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Using Colors" sheetId="1" r:id="rId2"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="Using Colors" sheetId="1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="125725"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>XLColor.Red</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XLColor.Byzantine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XLColor.FromArgb(0xFF00FF)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XLColor.FromArgb(16711935)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XLColor.FromArgb(255, 0, 255)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XLColor.FromArgb(0, 255, 0, 255)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XLColor.FromColor(Color.Red)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XLColor.FromHtml("#FF996515")</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XLColor.FromIndex(25)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XLColor.FromName("PowderBlue")</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XLColor.FromTheme(XLThemeColor.Accent1)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XLColor.FromTheme(XLThemeColor.Accent1, 0.5)</x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>XLColor.Red</t>
+  </si>
+  <si>
+    <t>XLColor.Byzantine</t>
+  </si>
+  <si>
+    <t>XLColor.FromArgb(0xFF00FF)</t>
+  </si>
+  <si>
+    <t>XLColor.FromArgb(16711935)</t>
+  </si>
+  <si>
+    <t>XLColor.FromArgb(255, 0, 255)</t>
+  </si>
+  <si>
+    <t>XLColor.FromArgb(0, 255, 0, 255)</t>
+  </si>
+  <si>
+    <t>XLColor.FromColor(Color.Red)</t>
+  </si>
+  <si>
+    <t>XLColor.FromHtml("#FF996515")</t>
+  </si>
+  <si>
+    <t>XLColor.FromIndex(25)</t>
+  </si>
+  <si>
+    <t>XLColor.FromName("PowderBlue")</t>
+  </si>
+  <si>
+    <t>XLColor.FromTheme(XLThemeColor.Accent1)</t>
+  </si>
+  <si>
+    <t>XLColor.FromTheme(XLThemeColor.Accent1, 0.5)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -441,94 +441,94 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:B18"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="45.282054" style="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:2">
-      <x:c r="A1" s="1"/>
-      <x:c r="B1" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:2">
-      <x:c r="A2" s="2"/>
-      <x:c r="B2" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:2">
-      <x:c r="A4" s="3"/>
-      <x:c r="B4" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:2">
-      <x:c r="A5" s="3"/>
-      <x:c r="B5" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:2">
-      <x:c r="A6" s="4"/>
-      <x:c r="B6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:2">
-      <x:c r="A7" s="3"/>
-      <x:c r="B7" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:2">
-      <x:c r="A9" s="1"/>
-      <x:c r="B9" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:2">
-      <x:c r="A11" s="5"/>
-      <x:c r="B11" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:2">
-      <x:c r="A13" s="6"/>
-      <x:c r="B13" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:2">
-      <x:c r="A15" s="7"/>
-      <x:c r="B15" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:2">
-      <x:c r="A17" s="8"/>
-      <x:c r="B17" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:2">
-      <x:c r="A18" s="9"/>
-      <x:c r="B18" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" style="0" customWidth="1" width="9.140625"/>
+    <col min="2" max="2" style="0" customWidth="1" width="45.282054"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1"/>
+      <c r="B1" s="0" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="3"/>
+      <c r="B4" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="3"/>
+      <c r="B5" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="4"/>
+      <c r="B6" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="3"/>
+      <c r="B7" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1"/>
+      <c r="B9" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="5"/>
+      <c r="B11" s="0" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="6"/>
+      <c r="B13" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="7"/>
+      <c r="B15" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="8"/>
+      <c r="B17" s="0" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="9"/>
+      <c r="B18" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>